--- a/docs/sdlc/40_test/WS2D-TM-001_トレーサビリティマトリクス.xlsx
+++ b/docs/sdlc/40_test/WS2D-TM-001_トレーサビリティマトリクス.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6:user.html,tenant.html</t>
+          <t>6:tenant.html,view-user-management.html</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>21:/admin/console,/api/admin/tenancy</t>
+          <t>21:/user-management,/api/admin/tenancy</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0（E2E未確認）</t>
+          <t>1:test_auth_tenant_e2e.py</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
